--- a/distribution_live_backup.xlsx
+++ b/distribution_live_backup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Backup" sheetId="1" r:id="rId1"/>
+    <sheet name="DistributionStatus" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/distribution_live_backup.xlsx
+++ b/distribution_live_backup.xlsx
@@ -6411,16 +6411,7 @@
         <v>Given</v>
       </c>
       <c r="G258" t="str">
-        <v>Ilyas</v>
-      </c>
-      <c r="H258" t="str">
-        <v>17/05/2026</v>
-      </c>
-      <c r="I258" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="J258" t="str">
-        <v>16:00:54</v>
+        <v/>
       </c>
     </row>
     <row r="259">
